--- a/output/hmb/ALP-HMB-SRC-NG-MEL.xlsx
+++ b/output/hmb/ALP-HMB-SRC-NG-MEL.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.0 | data a363d729afc29597 | 2026-09-28T03:15:47Z</t>
+          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-NG-MEL.xlsx
+++ b/output/hmb/ALP-HMB-SRC-NG-MEL.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a753f3df87285dba | 2026-09-28T14:33:04Z</t>
+          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-NG-MEL.xlsx
+++ b/output/hmb/ALP-HMB-SRC-NG-MEL.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.815024041710502</v>
+        <v>7.375024041710502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>213.3269759582895</v>
+        <v>213.7669759582895</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6956.435247815952</v>
+        <v>6942.116705415669</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51.7506434222939</v>
+        <v>51.85738230519195</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.850463803898906</v>
+        <v>3.652149475688692</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data 9f2d118f58330dd9 | 2026-09-28T19:00:37Z</t>
+          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>plant load (net, % of the reference case) 34.77 % of plant net output vs PG-11 &lt;= 40.00 (margin +13.07 %)</t>
+          <t>plant load (net, % of the reference case) 34.82 % of plant net output vs PG-11 &lt;= 40.00 (margin +12.95 %)</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-NG-MEL.xlsx
+++ b/output/hmb/ALP-HMB-SRC-NG-MEL.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -1831,6 +1831,56 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>source:SRC-IECE-0005</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>31</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fuel gas to the station preheater burners (water-bath heaters)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>fuel_gas</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FGS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PHB</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>15</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-21.08</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>preliminary</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>decision:DEC-EPCE-0014</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1870,7 +1920,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -2131,13 +2181,13 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>8.682</v>
+        <v>8.695</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2257,29 +2307,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>PHB</t>
         </is>
       </c>
       <c r="B14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>167.897</v>
+        <v>0.013</v>
       </c>
       <c r="D14" t="n">
-        <v>167.897</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>585.013</v>
+        <v>-0</v>
       </c>
       <c r="F14" t="n">
-        <v>584.6900000000001</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.322</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2289,29 +2339,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PIPE</t>
         </is>
       </c>
       <c r="B15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>167.897</v>
       </c>
       <c r="D15" t="n">
-        <v>10196.804</v>
+        <v>167.897</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>585.013</v>
       </c>
       <c r="F15" t="n">
-        <v>663.918</v>
+        <v>584.6900000000001</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-663.918</v>
+        <v>0.322</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2321,70 +2371,102 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="B16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>117.587</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>117.587</v>
+        <v>10196.804</v>
       </c>
       <c r="E16" t="n">
-        <v>422.784</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>326.836</v>
+        <v>663.918</v>
       </c>
       <c r="G16" t="n">
-        <v>95.94799999999999</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-663.918</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ST: shaft power (output / mechanical / generator efficiency)</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="B17" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>117.587</v>
+      </c>
+      <c r="D17" t="n">
+        <v>117.587</v>
+      </c>
+      <c r="E17" t="n">
+        <v>422.784</v>
+      </c>
+      <c r="F17" t="n">
+        <v>326.836</v>
+      </c>
+      <c r="G17" t="n">
+        <v>95.94799999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ST: shaft power (output / mechanical / generator efficiency)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>STK</t>
         </is>
       </c>
-      <c r="B17" t="b">
+      <c r="B18" t="b">
         <v>1</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
         <v>441.951</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
         <v>19.955</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>19.955</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2421,7 +2503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3573,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3691,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>412.2209152406198</v>
+        <v>412.8571465541679</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3639,7 +3721,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6942.116705415669</v>
+        <v>6952.831329218085</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3654,7 +3736,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51.85738230519195</v>
+        <v>51.77746776153788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3714,7 +3796,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8.682</v>
+        <v>8.695399999999999</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3729,7 +3811,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42668.42760457108</v>
+        <v>42734.28304455049</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3900,7 +3982,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data a6baea26d6584942 | 2026-09-29T02:54:45Z</t>
+          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-NG-MEL.xlsx
+++ b/output/hmb/ALP-HMB-SRC-NG-MEL.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.1.1 | data b6f4b950c7f3b7e0 | 2026-09-29T03:02:22Z</t>
+          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
         </is>
       </c>
     </row>

--- a/output/hmb/ALP-HMB-SRC-NG-MEL.xlsx
+++ b/output/hmb/ALP-HMB-SRC-NG-MEL.xlsx
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3982,7 +3982,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>engine hmb v1.2.0 | data 015d1cd1c6fdda54 | 2026-09-29T03:07:46Z</t>
+          <t>engine hmb v1.2.0 | data 6b60fce553593bf5 | 2026-09-29T03:49:51Z</t>
         </is>
       </c>
     </row>
@@ -4089,6 +4089,18 @@
         </is>
       </c>
       <c r="B11" t="inlineStr">
+        <is>
+          <t>CW temperature rise 3.83 K vs DP-CASE-0015 &lt;= 7.0 K (Condenser cooling water temperature rise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>plant load (net, % of the reference case) 34.82 % of plant net output vs PG-11 &lt;= 40.00 (margin +12.95 %)</t>
         </is>
